--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0126.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0126.xlsx
@@ -25491,7 +25491,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Giờ thì r?i ?i. Tạm biệt nhé.</t>
+          <t>Giờ thì Rời đi. Tạm biệt nhé.</t>
         </is>
       </c>
     </row>
